--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{229D25DE-340B-4432-86D8-A03D8515D2D2}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D87C844D-8D3F-4E60-A146-6243D6126401}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>userid</t>
   </si>
@@ -329,6 +329,12 @@
   </si>
   <si>
     <t>42580</t>
+  </si>
+  <si>
+    <t>정은숙</t>
+  </si>
+  <si>
+    <t>48883</t>
   </si>
 </sst>
 </file>
@@ -1760,11 +1766,15 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="A71" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="C71" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>정은숙.pdf</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D87C844D-8D3F-4E60-A146-6243D6126401}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A210812-23B3-46F2-A2EF-FEB4B93BC610}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3120" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>userid</t>
   </si>
@@ -335,6 +335,18 @@
   </si>
   <si>
     <t>48883</t>
+  </si>
+  <si>
+    <t>남궁석민</t>
+  </si>
+  <si>
+    <t>37078</t>
+  </si>
+  <si>
+    <t>이중배</t>
+  </si>
+  <si>
+    <t>78898</t>
   </si>
 </sst>
 </file>
@@ -1778,19 +1790,27 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
+      <c r="A72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="C72" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>남궁석민.pdf</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
+      <c r="A73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="C73" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>이중배.pdf</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A210812-23B3-46F2-A2EF-FEB4B93BC610}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8B791D0-8337-4448-9FA5-5D79D09B1D49}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3120" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>userid</t>
   </si>
@@ -347,6 +347,21 @@
   </si>
   <si>
     <t>78898</t>
+  </si>
+  <si>
+    <t>김예지</t>
+  </si>
+  <si>
+    <t>74476</t>
+  </si>
+  <si>
+    <t>이상희</t>
+  </si>
+  <si>
+    <t>안광린</t>
+  </si>
+  <si>
+    <t>19742</t>
   </si>
 </sst>
 </file>
@@ -1814,27 +1829,39 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
+      <c r="A74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="C74" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>김예지.pdf</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
+      <c r="A75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" s="1">
+        <v>31381</v>
+      </c>
       <c r="C75" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>이상희.pdf</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
+      <c r="A76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="C76" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>안광린.pdf</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8B791D0-8337-4448-9FA5-5D79D09B1D49}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68A0739E-156C-48A0-8AAE-456A1AFD6EA2}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>userid</t>
   </si>
@@ -362,6 +362,15 @@
   </si>
   <si>
     <t>19742</t>
+  </si>
+  <si>
+    <t>송관식</t>
+  </si>
+  <si>
+    <t>31699</t>
+  </si>
+  <si>
+    <t>장유진</t>
   </si>
 </sst>
 </file>
@@ -1865,19 +1874,27 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
+      <c r="A77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="C77" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>송관식.pdf</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
+      <c r="A78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" s="1">
+        <v>71897</v>
+      </c>
       <c r="C78" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>장유진.pdf</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68A0739E-156C-48A0-8AAE-456A1AFD6EA2}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B60B9F2-A3EF-4669-B8A9-07D25F7AB5B7}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>userid</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>장유진</t>
+  </si>
+  <si>
+    <t>김수정</t>
+  </si>
+  <si>
+    <t>57816</t>
   </si>
 </sst>
 </file>
@@ -1898,11 +1904,15 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
+      <c r="A79" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="C79" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>김수정.pdf</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B60B9F2-A3EF-4669-B8A9-07D25F7AB5B7}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D528DE6E-5B99-45BB-9C08-C1C3219D59F3}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>userid</t>
   </si>
@@ -377,6 +377,21 @@
   </si>
   <si>
     <t>57816</t>
+  </si>
+  <si>
+    <t>박창열</t>
+  </si>
+  <si>
+    <t>21829</t>
+  </si>
+  <si>
+    <t>현명한</t>
+  </si>
+  <si>
+    <t>정미근</t>
+  </si>
+  <si>
+    <t>윤웅섭</t>
   </si>
 </sst>
 </file>
@@ -1916,35 +1931,51 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
+      <c r="A80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="C80" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>박창열.pdf</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
+      <c r="A81" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46088</v>
+      </c>
       <c r="C81" t="str">
         <f t="shared" si="1"/>
-        <v>.pdf</v>
+        <v>현명한.pdf</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
+      <c r="A82" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B82" s="1">
+        <v>22257</v>
+      </c>
       <c r="C82" t="str">
         <f>A82&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>정미근.pdf</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46805</v>
+      </c>
       <c r="C83" t="str">
         <f t="shared" ref="C83:C117" si="2">A83&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>윤웅섭.pdf</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D528DE6E-5B99-45BB-9C08-C1C3219D59F3}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2790DAC-FEE1-43E0-99E8-96318961793B}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>userid</t>
   </si>
@@ -392,6 +392,30 @@
   </si>
   <si>
     <t>윤웅섭</t>
+  </si>
+  <si>
+    <t>신동윤</t>
+  </si>
+  <si>
+    <t>43499</t>
+  </si>
+  <si>
+    <t>정숙자</t>
+  </si>
+  <si>
+    <t>39490</t>
+  </si>
+  <si>
+    <t>임병희</t>
+  </si>
+  <si>
+    <t>06096</t>
+  </si>
+  <si>
+    <t>노성희</t>
+  </si>
+  <si>
+    <t>37638</t>
   </si>
 </sst>
 </file>
@@ -471,6 +495,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="출력"/>
@@ -1979,35 +2004,51 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
+      <c r="A84" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="C84" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>신동윤.pdf</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
+      <c r="A85" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="C85" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>정숙자.pdf</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
+      <c r="A86" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="C86" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>임병희.pdf</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
+      <c r="A87" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="C87" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>노성희.pdf</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2790DAC-FEE1-43E0-99E8-96318961793B}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E32B3139-AD38-4C51-8E00-9DD15BFFDC4E}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>userid</t>
   </si>
@@ -416,6 +416,18 @@
   </si>
   <si>
     <t>37638</t>
+  </si>
+  <si>
+    <t>강경화</t>
+  </si>
+  <si>
+    <t>32618</t>
+  </si>
+  <si>
+    <t>김규홍</t>
+  </si>
+  <si>
+    <t>74909</t>
   </si>
 </sst>
 </file>
@@ -2052,19 +2064,27 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
+      <c r="A88" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C88" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>강경화.pdf</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
+      <c r="A89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="C89" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김규홍.pdf</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E32B3139-AD38-4C51-8E00-9DD15BFFDC4E}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75FD26C5-D9D7-4DC9-8026-D7AC29D0EB48}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>userid</t>
   </si>
@@ -428,6 +428,24 @@
   </si>
   <si>
     <t>74909</t>
+  </si>
+  <si>
+    <t>최종진</t>
+  </si>
+  <si>
+    <t>50649</t>
+  </si>
+  <si>
+    <t>백승록</t>
+  </si>
+  <si>
+    <t>26941</t>
+  </si>
+  <si>
+    <t>장원식</t>
+  </si>
+  <si>
+    <t>39399</t>
   </si>
 </sst>
 </file>
@@ -2088,27 +2106,39 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
+      <c r="A90" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="C90" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>최종진.pdf</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
+      <c r="A91" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="C91" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>백승록.pdf</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
+      <c r="A92" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="C92" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>장원식.pdf</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75FD26C5-D9D7-4DC9-8026-D7AC29D0EB48}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DAF681A-E333-46D1-B7E0-54D7C934BD3B}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>userid</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>39399</t>
+  </si>
+  <si>
+    <t>조병훈</t>
+  </si>
+  <si>
+    <t>46002</t>
   </si>
 </sst>
 </file>
@@ -2142,11 +2148,15 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
+      <c r="A93" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="C93" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>조병훈.pdf</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DAF681A-E333-46D1-B7E0-54D7C934BD3B}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFE67CD-BCB3-48C5-AF54-830D19F4527A}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>userid</t>
   </si>
@@ -452,6 +452,18 @@
   </si>
   <si>
     <t>46002</t>
+  </si>
+  <si>
+    <t>김경민</t>
+  </si>
+  <si>
+    <t>57392</t>
+  </si>
+  <si>
+    <t>전유라</t>
+  </si>
+  <si>
+    <t>75176</t>
   </si>
 </sst>
 </file>
@@ -2160,19 +2172,27 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
+      <c r="A94" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="C94" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김경민.pdf</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
+      <c r="A95" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="C95" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>전유라.pdf</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BFE67CD-BCB3-48C5-AF54-830D19F4527A}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A71F6EE-C6CB-47A5-83AE-436696F1EF94}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>userid</t>
   </si>
@@ -464,6 +464,18 @@
   </si>
   <si>
     <t>75176</t>
+  </si>
+  <si>
+    <t>김성수</t>
+  </si>
+  <si>
+    <t>19197</t>
+  </si>
+  <si>
+    <t>임병인</t>
+  </si>
+  <si>
+    <t>50422</t>
   </si>
 </sst>
 </file>
@@ -2196,19 +2208,27 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
+      <c r="A96" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="C96" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김성수.pdf</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
+      <c r="A97" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="C97" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>임병인.pdf</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A71F6EE-C6CB-47A5-83AE-436696F1EF94}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DA0D7F-6BBB-484D-8A6C-74719CAAC052}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7140" yWindow="1425" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>userid</t>
   </si>
@@ -476,6 +476,18 @@
   </si>
   <si>
     <t>50422</t>
+  </si>
+  <si>
+    <t>김만철</t>
+  </si>
+  <si>
+    <t>46407</t>
+  </si>
+  <si>
+    <t>김은경</t>
+  </si>
+  <si>
+    <t>45890</t>
   </si>
 </sst>
 </file>
@@ -2232,19 +2244,27 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
+      <c r="A98" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="C98" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김만철.pdf</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
+      <c r="A99" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="C99" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김은경.pdf</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95DA0D7F-6BBB-484D-8A6C-74719CAAC052}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80FF2A7E-C4BA-411B-957E-7F78013F0293}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="1425" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>userid</t>
   </si>
@@ -488,6 +488,18 @@
   </si>
   <si>
     <t>45890</t>
+  </si>
+  <si>
+    <t>김미라</t>
+  </si>
+  <si>
+    <t>44418</t>
+  </si>
+  <si>
+    <t>김광섭</t>
+  </si>
+  <si>
+    <t>45441</t>
   </si>
 </sst>
 </file>
@@ -2268,19 +2280,27 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
+      <c r="A100" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>152</v>
+      </c>
       <c r="C100" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김미라.pdf</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
+      <c r="A101" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="C101" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김광섭.pdf</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80FF2A7E-C4BA-411B-957E-7F78013F0293}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F45531D-728E-4736-8FE2-054A445B229C}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>userid</t>
   </si>
@@ -500,6 +500,102 @@
   </si>
   <si>
     <t>45441</t>
+  </si>
+  <si>
+    <t>김영원</t>
+  </si>
+  <si>
+    <t>40501</t>
+  </si>
+  <si>
+    <t>김정수</t>
+  </si>
+  <si>
+    <t>김정수1</t>
+  </si>
+  <si>
+    <t>우종오</t>
+  </si>
+  <si>
+    <t>30160</t>
+  </si>
+  <si>
+    <t>고성권</t>
+  </si>
+  <si>
+    <t>25535</t>
+  </si>
+  <si>
+    <t>박해일</t>
+  </si>
+  <si>
+    <t>25385</t>
+  </si>
+  <si>
+    <t>이상준</t>
+  </si>
+  <si>
+    <t>21622</t>
+  </si>
+  <si>
+    <t>정남주</t>
+  </si>
+  <si>
+    <t>이현상</t>
+  </si>
+  <si>
+    <t>69021</t>
+  </si>
+  <si>
+    <t>정원석</t>
+  </si>
+  <si>
+    <t>67968</t>
+  </si>
+  <si>
+    <t>신성희</t>
+  </si>
+  <si>
+    <t>29322</t>
+  </si>
+  <si>
+    <t>여유정</t>
+  </si>
+  <si>
+    <t>26480</t>
+  </si>
+  <si>
+    <t>조찬원</t>
+  </si>
+  <si>
+    <t>32135</t>
+  </si>
+  <si>
+    <t>최소영</t>
+  </si>
+  <si>
+    <t>이미정</t>
+  </si>
+  <si>
+    <t>33702</t>
+  </si>
+  <si>
+    <t>김영현</t>
+  </si>
+  <si>
+    <t>41892</t>
+  </si>
+  <si>
+    <t>궁영균</t>
+  </si>
+  <si>
+    <t>32010</t>
+  </si>
+  <si>
+    <t>오세덕</t>
+  </si>
+  <si>
+    <t>37402</t>
   </si>
 </sst>
 </file>
@@ -2304,147 +2400,219 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
+      <c r="A102" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="C102" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김영원.pdf</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
+      <c r="A103" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" s="1">
+        <v>26338</v>
+      </c>
       <c r="C103" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김정수.pdf</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
+      <c r="A104" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B104" s="1">
+        <v>26322</v>
+      </c>
       <c r="C104" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김정수1.pdf</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
+      <c r="A105" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="C105" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>우종오.pdf</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
+      <c r="A106" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="C106" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>고성권.pdf</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
+      <c r="A107" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="C107" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>박해일.pdf</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
+      <c r="A108" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="C108" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>이상준.pdf</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
+      <c r="A109" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" s="1">
+        <v>40004</v>
+      </c>
       <c r="C109" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>정남주.pdf</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
+      <c r="A110" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="C110" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>이현상.pdf</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
+      <c r="A111" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="C111" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>정원석.pdf</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
+      <c r="A112" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="C112" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>신성희.pdf</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
+      <c r="A113" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="C113" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>여유정.pdf</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
+      <c r="A114" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="C114" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>조찬원.pdf</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
+      <c r="A115" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B115" s="1">
+        <v>80593</v>
+      </c>
       <c r="C115" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>최소영.pdf</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
+      <c r="A116" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="C116" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>이미정.pdf</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
+      <c r="A117" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>182</v>
+      </c>
       <c r="C117" t="str">
         <f t="shared" si="2"/>
-        <v>.pdf</v>
+        <v>김영현.pdf</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="A118" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>184</v>
+      </c>
       <c r="C118" t="str">
         <f>A118&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>궁영균.pdf</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="A119" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>186</v>
+      </c>
       <c r="C119" t="str">
         <f t="shared" ref="C119:C134" si="3">A119&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>오세덕.pdf</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F45531D-728E-4736-8FE2-054A445B229C}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC4EE4E-3A36-4496-B6E8-ACF82327C129}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>userid</t>
   </si>
@@ -596,6 +596,33 @@
   </si>
   <si>
     <t>37402</t>
+  </si>
+  <si>
+    <t>문경조</t>
+  </si>
+  <si>
+    <t>정유섭</t>
+  </si>
+  <si>
+    <t>18284</t>
+  </si>
+  <si>
+    <t>송진용</t>
+  </si>
+  <si>
+    <t>21433</t>
+  </si>
+  <si>
+    <t>김은영</t>
+  </si>
+  <si>
+    <t>44929</t>
+  </si>
+  <si>
+    <t>홍재현</t>
+  </si>
+  <si>
+    <t>조영은</t>
   </si>
 </sst>
 </file>
@@ -2616,51 +2643,75 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
+      <c r="A120" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B120" s="1">
+        <v>69576</v>
+      </c>
       <c r="C120" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>문경조.pdf</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
+      <c r="A121" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="C121" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>정유섭.pdf</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
+      <c r="A122" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="C122" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>송진용.pdf</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
+      <c r="A123" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>193</v>
+      </c>
       <c r="C123" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>김은영.pdf</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
+      <c r="A124" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B124" s="1">
+        <v>42615</v>
+      </c>
       <c r="C124" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>홍재현.pdf</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
+      <c r="A125" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B125" s="1">
+        <v>68799</v>
+      </c>
       <c r="C125" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>조영은.pdf</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC4EE4E-3A36-4496-B6E8-ACF82327C129}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38522AA5-0417-4AFF-AAFD-05634A3C4F95}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>userid</t>
   </si>
@@ -623,6 +623,9 @@
   </si>
   <si>
     <t>조영은</t>
+  </si>
+  <si>
+    <t>임철웅</t>
   </si>
 </sst>
 </file>
@@ -2715,11 +2718,15 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
+      <c r="A126" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B126" s="1">
+        <v>45381</v>
+      </c>
       <c r="C126" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>임철웅.pdf</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38522AA5-0417-4AFF-AAFD-05634A3C4F95}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2245889-1408-4153-A881-0759341CCD41}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>userid</t>
   </si>
@@ -626,6 +626,27 @@
   </si>
   <si>
     <t>임철웅</t>
+  </si>
+  <si>
+    <t>김정숙</t>
+  </si>
+  <si>
+    <t>문보성</t>
+  </si>
+  <si>
+    <t>55001</t>
+  </si>
+  <si>
+    <t>이강현</t>
+  </si>
+  <si>
+    <t>32289</t>
+  </si>
+  <si>
+    <t>김준영</t>
+  </si>
+  <si>
+    <t>70583</t>
   </si>
 </sst>
 </file>
@@ -2730,35 +2751,51 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
+      <c r="A127" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B127" s="1">
+        <v>42496</v>
+      </c>
       <c r="C127" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>김정숙.pdf</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
+      <c r="A128" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="C128" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>문보성.pdf</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
+      <c r="A129" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>201</v>
+      </c>
       <c r="C129" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>이강현.pdf</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
+      <c r="A130" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="C130" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>김준영.pdf</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2245889-1408-4153-A881-0759341CCD41}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54DD25BF-8906-4882-96A6-56AA0AEC34A7}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t>userid</t>
   </si>
@@ -647,6 +647,12 @@
   </si>
   <si>
     <t>70583</t>
+  </si>
+  <si>
+    <t>윤희지</t>
+  </si>
+  <si>
+    <t>오진혁</t>
   </si>
 </sst>
 </file>
@@ -2799,19 +2805,27 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
+      <c r="A131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B131" s="1">
+        <v>85349</v>
+      </c>
       <c r="C131" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>윤희지.pdf</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="1"/>
-      <c r="B132" s="1"/>
+      <c r="A132" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B132" s="1">
+        <v>82780</v>
+      </c>
       <c r="C132" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>오진혁.pdf</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54DD25BF-8906-4882-96A6-56AA0AEC34A7}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8417AE93-33D6-440C-9DCB-BAB4DE294DF6}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t>userid</t>
   </si>
@@ -653,6 +653,10 @@
   </si>
   <si>
     <t>오진혁</t>
+  </si>
+  <si>
+    <t>서하늘</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2829,11 +2833,15 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
+      <c r="A133" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B133" s="1">
+        <v>68271</v>
+      </c>
       <c r="C133" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>서하늘.pdf</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">

--- a/users_2026_backup.xlsx
+++ b/users_2026_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cb429d18e4db0f/Desktop/바탕화면/coding/pdf_printer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8417AE93-33D6-440C-9DCB-BAB4DE294DF6}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_2B59D2BFD320DC8176EC7B53541510344D078DDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{282325D7-80F1-45C8-91CF-9D4610AAF27F}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="13080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t>userid</t>
   </si>
@@ -657,6 +657,57 @@
   <si>
     <t>서하늘</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정해윤</t>
+  </si>
+  <si>
+    <t>24518</t>
+  </si>
+  <si>
+    <t>조동열</t>
+  </si>
+  <si>
+    <t>박은영</t>
+  </si>
+  <si>
+    <t>43222</t>
+  </si>
+  <si>
+    <t>강성하</t>
+  </si>
+  <si>
+    <t>43149</t>
+  </si>
+  <si>
+    <t>남준철</t>
+  </si>
+  <si>
+    <t>36465</t>
+  </si>
+  <si>
+    <t>박성웅</t>
+  </si>
+  <si>
+    <t>08277</t>
+  </si>
+  <si>
+    <t>박병민</t>
+  </si>
+  <si>
+    <t>51975</t>
+  </si>
+  <si>
+    <t>한형선</t>
+  </si>
+  <si>
+    <t>44209</t>
+  </si>
+  <si>
+    <t>피경희</t>
+  </si>
+  <si>
+    <t>41877</t>
   </si>
 </sst>
 </file>
@@ -706,13 +757,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2845,75 +2899,111 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
+      <c r="A134" t="s">
+        <v>207</v>
+      </c>
+      <c r="B134" t="s">
+        <v>208</v>
+      </c>
       <c r="C134" t="str">
         <f t="shared" si="3"/>
-        <v>.pdf</v>
+        <v>정해윤.pdf</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
+      <c r="A135" t="s">
+        <v>209</v>
+      </c>
+      <c r="B135" s="3">
+        <v>46742</v>
+      </c>
       <c r="C135" t="str">
         <f>A135&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>조동열.pdf</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
+      <c r="A136" t="s">
+        <v>210</v>
+      </c>
+      <c r="B136" t="s">
+        <v>211</v>
+      </c>
       <c r="C136" t="str">
         <f t="shared" ref="C136:C148" si="4">A136&amp;".pdf"</f>
-        <v>.pdf</v>
+        <v>박은영.pdf</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
+      <c r="A137" t="s">
+        <v>212</v>
+      </c>
+      <c r="B137" t="s">
+        <v>213</v>
+      </c>
       <c r="C137" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>강성하.pdf</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
+      <c r="A138" t="s">
+        <v>214</v>
+      </c>
+      <c r="B138" t="s">
+        <v>215</v>
+      </c>
       <c r="C138" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>남준철.pdf</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
+      <c r="A139" t="s">
+        <v>216</v>
+      </c>
+      <c r="B139" t="s">
+        <v>217</v>
+      </c>
       <c r="C139" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>박성웅.pdf</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
+      <c r="A140" t="s">
+        <v>218</v>
+      </c>
+      <c r="B140" t="s">
+        <v>219</v>
+      </c>
       <c r="C140" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>박병민.pdf</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
+      <c r="A141" t="s">
+        <v>220</v>
+      </c>
+      <c r="B141" t="s">
+        <v>221</v>
+      </c>
       <c r="C141" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>한형선.pdf</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
+      <c r="A142" t="s">
+        <v>222</v>
+      </c>
+      <c r="B142" t="s">
+        <v>223</v>
+      </c>
       <c r="C142" t="str">
         <f t="shared" si="4"/>
-        <v>.pdf</v>
+        <v>피경희.pdf</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
